--- a/data/trans_dic/P62A$otras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,91</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 28,38</t>
+          <t>8,34; 28,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 31,21</t>
+          <t>10,37; 32,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,95; 40,77</t>
+          <t>11,13; 42,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,98</t>
+          <t>0,0; 16,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 39,07</t>
+          <t>16,97; 39,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 43,5</t>
+          <t>17,54; 44,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,45; 45,12</t>
+          <t>18,63; 42,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,2</t>
+          <t>0,88; 7,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 29,51</t>
+          <t>14,66; 30,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 33,67</t>
+          <t>16,74; 34,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 37,66</t>
+          <t>17,86; 38,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,86</t>
+          <t>2,35; 11,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 18,88</t>
+          <t>7,94; 19,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 25,39</t>
+          <t>11,47; 25,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 15,84</t>
+          <t>2,87; 15,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 29,33</t>
+          <t>10,55; 28,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,75</t>
+          <t>2,25; 13,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 28,88</t>
+          <t>15,84; 28,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,61</t>
+          <t>1,87; 7,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 16,49</t>
+          <t>7,15; 16,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,7</t>
+          <t>6,41; 14,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 24,31</t>
+          <t>14,95; 24,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 14,06</t>
+          <t>1,2; 13,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,32</t>
+          <t>2,85; 12,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>0,0; 10,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,91</t>
+          <t>2,6; 15,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 18,36</t>
+          <t>3,84; 18,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,12</t>
+          <t>5,18; 14,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,76</t>
+          <t>2,6; 12,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,19</t>
+          <t>2,25; 9,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,25</t>
+          <t>4,91; 11,89</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 10,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 12,91</t>
+          <t>3,01; 13,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,78</t>
+          <t>1,06; 10,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 21,47</t>
+          <t>5,46; 22,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,56</t>
+          <t>3,03; 16,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 16,96</t>
+          <t>4,02; 17,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,77</t>
+          <t>1,12; 9,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 16,39</t>
+          <t>5,09; 15,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,89</t>
+          <t>2,17; 10,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,58</t>
+          <t>4,82; 12,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,6</t>
+          <t>1,62; 7,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 16,76</t>
+          <t>6,67; 16,16</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 11,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,48</t>
+          <t>2,01; 18,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,47</t>
+          <t>1,39; 11,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,99; 54,67</t>
+          <t>30,44; 54,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,63</t>
+          <t>0,0; 15,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 27,49</t>
+          <t>6,31; 27,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,99; 63,1</t>
+          <t>37,27; 63,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,86; 32,27</t>
+          <t>16,87; 31,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,85</t>
+          <t>6,08; 19,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,56; 33,82</t>
+          <t>17,7; 34,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 39,65</t>
+          <t>24,63; 38,65</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,54</t>
+          <t>0,0; 9,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,03</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,21</t>
+          <t>1,3; 11,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,62; 22,75</t>
+          <t>8,01; 21,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,41</t>
+          <t>0,0; 18,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 17,91</t>
+          <t>3,24; 18,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 19,93</t>
+          <t>2,06; 21,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,85</t>
+          <t>2,64; 11,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,6</t>
+          <t>0,93; 9,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,05</t>
+          <t>1,52; 8,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,02</t>
+          <t>2,51; 11,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 16,55</t>
+          <t>6,44; 16,02</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 13,54</t>
+          <t>3,92; 14,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,88</t>
+          <t>2,82; 10,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,12; 28,55</t>
+          <t>15,9; 27,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,76</t>
+          <t>0,82; 8,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 16,24</t>
+          <t>5,45; 16,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 19,17</t>
+          <t>7,95; 20,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 16,91</t>
+          <t>1,58; 16,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,07</t>
+          <t>0,43; 4,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 12,94</t>
+          <t>5,61; 12,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 13,97</t>
+          <t>6,84; 13,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 19,47</t>
+          <t>3,69; 20,03</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,79</t>
+          <t>2,67; 9,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,94</t>
+          <t>1,91; 8,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64,29; 75,09</t>
+          <t>63,72; 74,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,22</t>
+          <t>0,95; 8,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 18,82</t>
+          <t>7,93; 18,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,4; 19,46</t>
+          <t>8,49; 19,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,98; 43,9</t>
+          <t>32,66; 43,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,86</t>
+          <t>0,42; 3,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,04</t>
+          <t>5,89; 12,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,53</t>
+          <t>5,86; 11,8</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,8; 58,83</t>
+          <t>51,15; 59,15</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,74</t>
+          <t>0,38; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,9</t>
+          <t>5,23; 8,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,29</t>
+          <t>4,98; 8,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27,24; 33,18</t>
+          <t>27,09; 33,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,74</t>
+          <t>3,0; 6,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,5; 15,47</t>
+          <t>10,42; 15,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,48</t>
+          <t>12,25; 17,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,28; 21,49</t>
+          <t>8,34; 21,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,53</t>
+          <t>1,83; 3,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,3</t>
+          <t>8,13; 11,32</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,01</t>
+          <t>8,88; 11,91</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,7; 26,17</t>
+          <t>14,67; 26,29</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4702</t>
+          <t>0; 5533</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5975; 21592</t>
+          <t>6348; 22053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6087; 18178</t>
+          <t>6039; 19188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2413; 9886</t>
+          <t>2698; 10267</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5677</t>
+          <t>0; 5705</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11266; 26885</t>
+          <t>11677; 27124</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10020; 23916</t>
+          <t>9642; 24415</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5434; 14049</t>
+          <t>5802; 13210</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>781; 7243</t>
+          <t>778; 6656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20664; 42752</t>
+          <t>21245; 44484</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19088; 38128</t>
+          <t>18952; 38880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9462; 20859</t>
+          <t>9891; 21244</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5435</t>
+          <t>0; 6074</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3832; 15697</t>
+          <t>3114; 15112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10954; 28051</t>
+          <t>11790; 28424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15394; 34231</t>
+          <t>15467; 34695</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2862; 12547</t>
+          <t>2273; 11973</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9401; 26069</t>
+          <t>9376; 25351</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2137; 12596</t>
+          <t>2060; 12431</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20333; 35247</t>
+          <t>19333; 34361</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3830; 15231</t>
+          <t>3746; 14588</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15896; 36475</t>
+          <t>15809; 36824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16095; 35303</t>
+          <t>15397; 35483</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38754; 62440</t>
+          <t>38393; 63264</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>994; 11564</t>
+          <t>983; 11416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>0; 5649</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1866; 11305</t>
+          <t>2616; 11345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6351</t>
+          <t>0; 7062</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2004; 12019</t>
+          <t>1966; 11656</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3250; 14669</t>
+          <t>3067; 14463</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4381; 12658</t>
+          <t>4336; 12153</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6781</t>
+          <t>0; 6765</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4826; 18563</t>
+          <t>4097; 18995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3967; 15613</t>
+          <t>3823; 16732</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8378; 19743</t>
+          <t>8626; 20874</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5531</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3136; 13216</t>
+          <t>3083; 13539</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1043; 10404</t>
+          <t>1022; 9721</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4099; 16962</t>
+          <t>4317; 17686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1762; 10092</t>
+          <t>1964; 10530</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4582; 17080</t>
+          <t>4053; 17791</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>868; 7568</t>
+          <t>865; 7273</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4102; 13230</t>
+          <t>4111; 12707</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2942; 13337</t>
+          <t>2922; 13723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9338; 27580</t>
+          <t>9799; 25793</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2958; 13219</t>
+          <t>2824; 12509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11199; 26772</t>
+          <t>10660; 25808</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5555</t>
+          <t>0; 5007</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1005; 9234</t>
+          <t>1002; 9407</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>919; 7654</t>
+          <t>929; 7535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9415; 17164</t>
+          <t>9558; 17171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4763</t>
+          <t>0; 5265</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3720; 12927</t>
+          <t>2965; 13015</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20014; 36091</t>
+          <t>21319; 36249</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7024; 13443</t>
+          <t>7026; 13284</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6435</t>
+          <t>0; 6669</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5841; 18284</t>
+          <t>5898; 18432</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21764; 41903</t>
+          <t>21938; 42224</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18079; 28968</t>
+          <t>17992; 28238</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6665</t>
+          <t>0; 5954</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 5549</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>951; 8286</t>
+          <t>962; 8490</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6092; 18188</t>
+          <t>6403; 17505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 8275</t>
+          <t>0; 8893</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1946; 10766</t>
+          <t>1949; 10986</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>913; 8826</t>
+          <t>912; 9322</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1809; 7102</t>
+          <t>1583; 6870</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1023; 10636</t>
+          <t>1028; 10871</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2012; 12170</t>
+          <t>2042; 11777</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2926; 13025</t>
+          <t>2970; 13533</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9664; 23151</t>
+          <t>9010; 22404</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1864</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5713; 21549</t>
+          <t>6241; 22364</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5011; 16716</t>
+          <t>4328; 16355</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25584; 45294</t>
+          <t>25232; 44299</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1191; 10421</t>
+          <t>973; 10148</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8258; 24377</t>
+          <t>8182; 24702</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12441; 29280</t>
+          <t>12141; 30732</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5527; 58156</t>
+          <t>5418; 57041</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1143; 10652</t>
+          <t>1125; 10680</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18003; 40009</t>
+          <t>17350; 38912</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20218; 42808</t>
+          <t>20956; 42358</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16070; 97870</t>
+          <t>18545; 100674</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5308; 19062</t>
+          <t>5199; 17904</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4169; 16955</t>
+          <t>4072; 17576</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129605; 151387</t>
+          <t>128464; 150801</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1244; 10581</t>
+          <t>1222; 10506</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12628; 29146</t>
+          <t>12278; 28891</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15028; 34814</t>
+          <t>15188; 34448</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>57559; 76608</t>
+          <t>57002; 76038</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1213; 11468</t>
+          <t>1236; 11429</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20626; 42091</t>
+          <t>20599; 43370</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22444; 45270</t>
+          <t>22982; 46319</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>191074; 221242</t>
+          <t>192364; 222478</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2732; 12874</t>
+          <t>2795; 13718</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>45598; 77561</t>
+          <t>45583; 76997</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44216; 74670</t>
+          <t>44849; 75868</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>218331; 265915</t>
+          <t>217117; 264657</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18477; 38851</t>
+          <t>17283; 39179</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>78344; 115435</t>
+          <t>77718; 118426</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89612; 128867</t>
+          <t>90297; 132020</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>77601; 201462</t>
+          <t>78212; 203284</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23706; 46446</t>
+          <t>23990; 48784</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>132079; 182666</t>
+          <t>131474; 183044</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>142716; 196679</t>
+          <t>145433; 195121</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>255724; 455137</t>
+          <t>255174; 457237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$otras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 28,98</t>
+          <t>8,9; 28,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 32,94</t>
+          <t>9,64; 33,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 42,35</t>
+          <t>15,04; 46,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,06</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 39,42</t>
+          <t>18,19; 40,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 44,41</t>
+          <t>18,44; 44,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 42,42</t>
+          <t>16,94; 41,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,54</t>
+          <t>0,9; 9,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,66; 30,7</t>
+          <t>15,45; 30,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 34,34</t>
+          <t>16,47; 32,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 38,36</t>
+          <t>18,13; 37,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 11,42</t>
+          <t>2,26; 11,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 19,13</t>
+          <t>7,77; 18,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 25,73</t>
+          <t>10,66; 24,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 15,12</t>
+          <t>3,57; 15,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 28,52</t>
+          <t>11,46; 29,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,57</t>
+          <t>2,23; 13,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 28,16</t>
+          <t>15,89; 27,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,29</t>
+          <t>1,83; 7,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 16,65</t>
+          <t>6,96; 16,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 14,77</t>
+          <t>6,75; 15,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,95; 24,63</t>
+          <t>14,65; 23,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 13,88</t>
+          <t>1,21; 13,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,36</t>
+          <t>2,9; 11,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,63</t>
+          <t>0,0; 10,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 15,43</t>
+          <t>2,63; 15,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 18,1</t>
+          <t>3,64; 17,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 14,52</t>
+          <t>5,88; 16,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 12,04</t>
+          <t>3,03; 11,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,85</t>
+          <t>2,21; 9,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,89</t>
+          <t>5,11; 11,82</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 9,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 13,22</t>
+          <t>3,06; 14,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,07</t>
+          <t>1,07; 9,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 22,38</t>
+          <t>5,3; 21,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 16,24</t>
+          <t>3,07; 16,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 17,67</t>
+          <t>4,01; 17,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,39</t>
+          <t>1,14; 9,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 15,75</t>
+          <t>4,99; 16,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 10,18</t>
+          <t>2,17; 10,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 12,7</t>
+          <t>4,89; 13,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,19</t>
+          <t>1,67; 7,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 16,16</t>
+          <t>6,62; 16,23</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,06</t>
+          <t>0,0; 10,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,83</t>
+          <t>2,03; 18,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,29</t>
+          <t>1,38; 11,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,44; 54,69</t>
+          <t>32,08; 56,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,07</t>
+          <t>0,0; 14,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 27,68</t>
+          <t>5,95; 26,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,27; 63,37</t>
+          <t>36,22; 62,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,87; 31,89</t>
+          <t>16,59; 31,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,31</t>
+          <t>0,0; 7,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 19,01</t>
+          <t>5,24; 18,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 34,07</t>
+          <t>18,13; 33,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,63; 38,65</t>
+          <t>25,54; 39,39</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,48</t>
+          <t>1,27; 12,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 21,9</t>
+          <t>8,05; 21,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,71</t>
+          <t>0,0; 18,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,28</t>
+          <t>3,24; 18,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 21,04</t>
+          <t>2,03; 19,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,46</t>
+          <t>3,07; 12,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,82</t>
+          <t>0,93; 10,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,76</t>
+          <t>1,54; 9,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,45</t>
+          <t>2,4; 11,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,44; 16,02</t>
+          <t>6,76; 15,41</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 14,06</t>
+          <t>3,73; 13,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,64</t>
+          <t>2,83; 11,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,9; 27,92</t>
+          <t>16,79; 28,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,53</t>
+          <t>0,95; 9,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 16,45</t>
+          <t>5,03; 16,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 20,13</t>
+          <t>8,08; 19,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 16,59</t>
+          <t>11,47; 20,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,08</t>
+          <t>0,46; 4,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,58</t>
+          <t>5,81; 12,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 13,83</t>
+          <t>6,83; 13,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 20,03</t>
+          <t>15,57; 23,04</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -1702,57 +1702,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,2</t>
+          <t>2,66; 9,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 8,23</t>
+          <t>1,93; 8,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63,72; 74,8</t>
+          <t>64,51; 75,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,17</t>
+          <t>0,96; 8,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,66</t>
+          <t>7,95; 18,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,49; 19,25</t>
+          <t>8,26; 18,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,66; 43,57</t>
+          <t>33,06; 43,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,85</t>
+          <t>0,41; 3,84</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,41</t>
+          <t>5,86; 11,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,8</t>
+          <t>5,74; 11,67</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,15; 59,15</t>
+          <t>50,51; 58,83</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,86</t>
+          <t>0,37; 1,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,84</t>
+          <t>5,1; 8,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,42</t>
+          <t>5,02; 8,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27,09; 33,02</t>
+          <t>27,97; 33,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,8</t>
+          <t>3,25; 6,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,87</t>
+          <t>10,59; 15,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,25; 17,91</t>
+          <t>12,05; 17,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,34; 21,68</t>
+          <t>18,69; 23,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,71</t>
+          <t>1,8; 3,56</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,32</t>
+          <t>8,15; 11,23</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,88; 11,91</t>
+          <t>8,79; 11,82</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,67; 26,29</t>
+          <t>24,34; 28,08</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>15546</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5533</t>
+          <t>0; 4743</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6348; 22053</t>
+          <t>6768; 21818</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6039; 19188</t>
+          <t>5616; 19319</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2698; 10267</t>
+          <t>3806; 11755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5705</t>
+          <t>0; 5734</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11677; 27124</t>
+          <t>12519; 28177</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9642; 24415</t>
+          <t>10140; 24653</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5802; 13210</t>
+          <t>5313; 13009</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>778; 6656</t>
+          <t>792; 8263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21245; 44484</t>
+          <t>22390; 44829</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18952; 38880</t>
+          <t>18648; 36877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9891; 21244</t>
+          <t>10273; 21305</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26530</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>50713</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6074</t>
+          <t>0; 6160</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3114; 15112</t>
+          <t>2985; 15384</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11790; 28424</t>
+          <t>11545; 27919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15467; 34695</t>
+          <t>15247; 34830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2273; 11973</t>
+          <t>2826; 12128</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9376; 25351</t>
+          <t>10187; 25858</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2060; 12431</t>
+          <t>2047; 12799</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19333; 34361</t>
+          <t>20176; 34698</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3746; 14588</t>
+          <t>3669; 14586</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15809; 36824</t>
+          <t>15388; 36296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15397; 35483</t>
+          <t>16213; 36088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38393; 63264</t>
+          <t>39552; 64074</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>14371</t>
         </is>
       </c>
     </row>
@@ -2630,57 +2630,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>983; 11416</t>
+          <t>992; 11369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5649</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2616; 11345</t>
+          <t>2614; 10553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7062</t>
+          <t>0; 7056</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1966; 11656</t>
+          <t>1988; 11866</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3067; 14463</t>
+          <t>2912; 14091</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4336; 12153</t>
+          <t>5066; 14055</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6765</t>
+          <t>0; 6970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4097; 18995</t>
+          <t>4774; 18884</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3823; 16732</t>
+          <t>3755; 15786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8626; 20874</t>
+          <t>9008; 20827</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>18792</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7081</t>
+          <t>0; 6395</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3083; 13539</t>
+          <t>3136; 14447</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1022; 9721</t>
+          <t>1031; 9056</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4317; 17686</t>
+          <t>4715; 19185</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1964; 10530</t>
+          <t>1990; 10762</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4053; 17791</t>
+          <t>4039; 17341</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>865; 7273</t>
+          <t>879; 7652</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4111; 12707</t>
+          <t>4298; 14033</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2922; 13723</t>
+          <t>2930; 13493</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9799; 25793</t>
+          <t>9939; 26734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2824; 12509</t>
+          <t>2911; 13118</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10660; 25808</t>
+          <t>11577; 28400</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>24756</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5007</t>
+          <t>0; 4953</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1002; 9407</t>
+          <t>1013; 9329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>929; 7535</t>
+          <t>923; 7705</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9558; 17171</t>
+          <t>10733; 18833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5265</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2965; 13015</t>
+          <t>2797; 12256</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21319; 36249</t>
+          <t>20717; 35968</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7026; 13284</t>
+          <t>7179; 13699</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6669</t>
+          <t>0; 5851</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5898; 18432</t>
+          <t>5080; 17785</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21938; 42224</t>
+          <t>22469; 41232</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17992; 28238</t>
+          <t>19596; 30223</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>14162</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5954</t>
+          <t>0; 5331</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5549</t>
+          <t>0; 5166</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>962; 8490</t>
+          <t>942; 9114</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6403; 17505</t>
+          <t>6365; 16924</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 8893</t>
+          <t>0; 8851</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1949; 10986</t>
+          <t>1946; 10908</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>912; 9322</t>
+          <t>897; 8700</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1583; 6870</t>
+          <t>1881; 7406</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1028; 10871</t>
+          <t>1031; 11372</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2042; 11777</t>
+          <t>2064; 12206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2970; 13533</t>
+          <t>2838; 13183</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9010; 22404</t>
+          <t>9489; 21637</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55261</t>
+          <t>68871</t>
         </is>
       </c>
     </row>
@@ -3462,57 +3462,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6241; 22364</t>
+          <t>5934; 21278</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4328; 16355</t>
+          <t>4343; 17134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25232; 44299</t>
+          <t>31975; 53893</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>973; 10148</t>
+          <t>1135; 10759</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8182; 24702</t>
+          <t>7558; 24090</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12141; 30732</t>
+          <t>12334; 30358</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5418; 57041</t>
+          <t>19331; 34722</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1125; 10680</t>
+          <t>1191; 10906</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17350; 38912</t>
+          <t>17952; 39398</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20956; 42358</t>
+          <t>20912; 41819</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18545; 100674</t>
+          <t>55886; 82733</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>140138</t>
+          <t>155998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>66705</t>
+          <t>75385</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>206843</t>
+          <t>231383</t>
         </is>
       </c>
     </row>
@@ -3670,57 +3670,57 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5199; 17904</t>
+          <t>5184; 18422</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4072; 17576</t>
+          <t>4112; 17308</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128464; 150801</t>
+          <t>144575; 168435</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1222; 10506</t>
+          <t>1241; 11172</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12278; 28891</t>
+          <t>12308; 29122</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15188; 34448</t>
+          <t>14787; 32625</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>57002; 76038</t>
+          <t>66172; 87460</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1236; 11429</t>
+          <t>1222; 11392</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20599; 43370</t>
+          <t>20469; 41231</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22982; 46319</t>
+          <t>22513; 45808</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>192364; 222478</t>
+          <t>214283; 249602</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>269735</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>152188</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>394527</t>
+          <t>438594</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2795; 13718</t>
+          <t>2753; 12746</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>45583; 76997</t>
+          <t>44464; 77035</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44849; 75868</t>
+          <t>45244; 76195</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>217117; 264657</t>
+          <t>244560; 294498</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17283; 39179</t>
+          <t>18706; 40171</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77718; 118426</t>
+          <t>78999; 119181</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90297; 132020</t>
+          <t>88792; 129165</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>78212; 203284</t>
+          <t>150263; 186524</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23990; 48784</t>
+          <t>23649; 46759</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>131474; 183044</t>
+          <t>131836; 181554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>145433; 195121</t>
+          <t>144074; 193592</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>255174; 457237</t>
+          <t>408488; 471254</t>
         </is>
       </c>
     </row>
